--- a/Excel_export/2025T143_heating120.xlsx
+++ b/Excel_export/2025T143_heating120.xlsx
@@ -917,16 +917,16 @@
     <t>UTC timestamp in ISO 8601 format</t>
   </si>
   <si>
-    <t>Raw GPS latitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS latitude on this data time axis</t>
   </si>
   <si>
-    <t>Raw GPS longitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS longitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled latitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled latitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled longitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled longitude on this data time axis</t>
   </si>
   <si>
     <t>1=original; 2=interpolated; 3=invalid; 4=edge extrapolated; 5=long-gap filled</t>
@@ -2101,10 +2101,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>83.911900000000003</v>
+        <v>83.518900000000002</v>
       </c>
       <c r="C2" s="0">
-        <v>24.003499999999999</v>
+        <v>29.547999999999998</v>
       </c>
       <c r="D2" s="0">
         <v>83.890699999999995</v>
@@ -2858,10 +2858,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>83.687799999999996</v>
+        <v>83.865399999999994</v>
       </c>
       <c r="C3" s="0">
-        <v>29.649799999999999</v>
+        <v>25.665199999999999</v>
       </c>
       <c r="D3" s="0">
         <v>83.878500000000003</v>
@@ -3615,10 +3615,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>83.639200000000002</v>
+        <v>83.685699999999997</v>
       </c>
       <c r="C4" s="0">
-        <v>29.009499999999999</v>
+        <v>28.8964</v>
       </c>
       <c r="D4" s="0">
         <v>83.865700000000004</v>
@@ -4372,10 +4372,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>83.802199999999999</v>
+        <v>83.770499999999998</v>
       </c>
       <c r="C5" s="0">
-        <v>26.8642</v>
+        <v>26.712700000000002</v>
       </c>
       <c r="D5" s="0">
         <v>83.802199999999999</v>
@@ -5129,10 +5129,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>83.711200000000005</v>
+        <v>83.659000000000006</v>
       </c>
       <c r="C6" s="0">
-        <v>25.7423</v>
+        <v>26.565100000000001</v>
       </c>
       <c r="D6" s="0">
         <v>83.630099999999999</v>
@@ -5886,10 +5886,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>83.656300000000002</v>
+        <v>83.579400000000007</v>
       </c>
       <c r="C7" s="0">
-        <v>25.1218</v>
+        <v>26.565100000000001</v>
       </c>
       <c r="D7" s="0">
         <v>83.485100000000003</v>
@@ -6643,10 +6643,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>83.384100000000004</v>
+        <v>83.415700000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>27.829799999999999</v>
+        <v>27.2638</v>
       </c>
       <c r="D8" s="0">
         <v>83.382800000000003</v>
@@ -7400,10 +7400,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>83.436700000000002</v>
+        <v>83.351299999999995</v>
       </c>
       <c r="C9" s="0">
-        <v>27.031700000000001</v>
+        <v>27.6721</v>
       </c>
       <c r="D9" s="0">
         <v>83.399299999999997</v>
@@ -8157,10 +8157,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>83.831299999999999</v>
+        <v>83.431899999999999</v>
       </c>
       <c r="C10" s="0">
-        <v>22.2562</v>
+        <v>26.985299999999999</v>
       </c>
       <c r="D10" s="0">
         <v>83.399199999999993</v>
@@ -8914,10 +8914,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>83.271799999999999</v>
+        <v>83.938599999999994</v>
       </c>
       <c r="C11" s="0">
-        <v>27.659400000000002</v>
+        <v>19.722300000000001</v>
       </c>
       <c r="D11" s="0">
         <v>83.303100000000001</v>
@@ -9671,10 +9671,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>83.139600000000002</v>
+        <v>83.156400000000005</v>
       </c>
       <c r="C12" s="0">
-        <v>27.772500000000001</v>
+        <v>27.506499999999999</v>
       </c>
       <c r="D12" s="0">
         <v>83.139700000000005</v>
@@ -10428,10 +10428,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>82.959500000000006</v>
+        <v>82.964299999999994</v>
       </c>
       <c r="C13" s="0">
-        <v>28.0046</v>
+        <v>28.003699999999998</v>
       </c>
       <c r="D13" s="0">
         <v>82.959599999999995</v>
@@ -11185,10 +11185,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>82.821100000000001</v>
+        <v>82.898200000000003</v>
       </c>
       <c r="C14" s="0">
-        <v>27.756</v>
+        <v>27.083500000000001</v>
       </c>
       <c r="D14" s="0">
         <v>82.817400000000006</v>
@@ -11942,10 +11942,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>82.710899999999995</v>
+        <v>82.707499999999996</v>
       </c>
       <c r="C15" s="0">
-        <v>26.979800000000001</v>
+        <v>26.9436</v>
       </c>
       <c r="D15" s="0">
         <v>82.707499999999996</v>
@@ -12699,10 +12699,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>82.623199999999997</v>
+        <v>82.607699999999994</v>
       </c>
       <c r="C16" s="0">
-        <v>26.3127</v>
+        <v>26.565100000000001</v>
       </c>
       <c r="D16" s="0">
         <v>82.623500000000007</v>
@@ -13456,10 +13456,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>82.514600000000002</v>
+        <v>82.543999999999997</v>
       </c>
       <c r="C17" s="0">
-        <v>27.459299999999999</v>
+        <v>26.935500000000001</v>
       </c>
       <c r="D17" s="0">
         <v>82.511600000000001</v>
@@ -14213,10 +14213,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>82.493399999999994</v>
+        <v>82.5244</v>
       </c>
       <c r="C18" s="0">
-        <v>28.285799999999998</v>
+        <v>28.412700000000001</v>
       </c>
       <c r="D18" s="0">
         <v>82.509900000000002</v>
@@ -14970,10 +14970,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>82.507599999999996</v>
+        <v>82.521500000000003</v>
       </c>
       <c r="C19" s="0">
-        <v>28.6586</v>
+        <v>29.027899999999999</v>
       </c>
       <c r="D19" s="0">
         <v>82.500100000000003</v>
@@ -15727,10 +15727,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>82.443600000000004</v>
+        <v>82.507499999999993</v>
       </c>
       <c r="C20" s="0">
-        <v>29.020199999999999</v>
+        <v>28.654299999999999</v>
       </c>
       <c r="D20" s="0">
         <v>82.486599999999996</v>
@@ -16484,10 +16484,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>82.403700000000001</v>
+        <v>82.385099999999994</v>
       </c>
       <c r="C21" s="0">
-        <v>30.092300000000002</v>
+        <v>30.314800000000002</v>
       </c>
       <c r="D21" s="0">
         <v>82.418700000000001</v>
@@ -17241,10 +17241,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>82.447100000000006</v>
+        <v>82.458699999999993</v>
       </c>
       <c r="C22" s="0">
-        <v>30.601700000000001</v>
+        <v>30.963799999999999</v>
       </c>
       <c r="D22" s="0">
         <v>82.446399999999997</v>
@@ -17998,10 +17998,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>82.482200000000006</v>
+        <v>82.501000000000005</v>
       </c>
       <c r="C23" s="0">
-        <v>31.7133</v>
+        <v>31.4816</v>
       </c>
       <c r="D23" s="0">
         <v>82.482399999999998</v>
@@ -18755,10 +18755,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>82.484899999999996</v>
+        <v>82.466499999999996</v>
       </c>
       <c r="C24" s="0">
-        <v>32.692799999999998</v>
+        <v>32.932200000000002</v>
       </c>
       <c r="D24" s="0">
         <v>82.493899999999996</v>
@@ -19512,10 +19512,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>82.614400000000003</v>
+        <v>82.644499999999994</v>
       </c>
       <c r="C25" s="0">
-        <v>33.6783</v>
+        <v>33.845300000000002</v>
       </c>
       <c r="D25" s="0">
         <v>82.615099999999998</v>
@@ -20269,10 +20269,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>82.875</v>
+        <v>82.874600000000001</v>
       </c>
       <c r="C26" s="0">
-        <v>34.733899999999998</v>
+        <v>34.731699999999996</v>
       </c>
       <c r="D26" s="0">
         <v>82.875</v>
@@ -21026,10 +21026,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>83.079700000000003</v>
+        <v>83.053299999999993</v>
       </c>
       <c r="C27" s="0">
-        <v>35.8735</v>
+        <v>35.744300000000003</v>
       </c>
       <c r="D27" s="0">
         <v>83.0822</v>
@@ -21783,10 +21783,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>83.123800000000003</v>
+        <v>83.123599999999996</v>
       </c>
       <c r="C28" s="0">
-        <v>35.431600000000003</v>
+        <v>35.433300000000003</v>
       </c>
       <c r="D28" s="0">
         <v>83.123800000000003</v>
@@ -22540,10 +22540,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>83.231499999999997</v>
+        <v>83.256100000000004</v>
       </c>
       <c r="C29" s="0">
-        <v>35.717700000000001</v>
+        <v>35.466799999999999</v>
       </c>
       <c r="D29" s="0">
         <v>83.231399999999994</v>
@@ -23297,10 +23297,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>83.272099999999995</v>
+        <v>83.272000000000006</v>
       </c>
       <c r="C30" s="0">
-        <v>36.320399999999999</v>
+        <v>36.319600000000001</v>
       </c>
       <c r="D30" s="0">
         <v>83.300600000000003</v>
@@ -24054,10 +24054,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>83.357900000000001</v>
+        <v>83.357699999999994</v>
       </c>
       <c r="C31" s="0">
-        <v>36.868099999999998</v>
+        <v>36.869900000000001</v>
       </c>
       <c r="D31" s="0">
         <v>83.357799999999997</v>
@@ -24811,10 +24811,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>83.4148</v>
+        <v>83.436000000000007</v>
       </c>
       <c r="C32" s="0">
-        <v>37.246400000000001</v>
+        <v>36.9953</v>
       </c>
       <c r="D32" s="0">
         <v>83.436099999999996</v>
@@ -25568,10 +25568,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>83.574700000000007</v>
+        <v>83.492699999999999</v>
       </c>
       <c r="C33" s="0">
-        <v>37.510300000000001</v>
+        <v>37.375799999999998</v>
       </c>
       <c r="D33" s="0">
         <v>83.521000000000001</v>
@@ -26325,10 +26325,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>83.493200000000002</v>
+        <v>83.5749</v>
       </c>
       <c r="C34" s="0">
-        <v>37.376100000000001</v>
+        <v>37.510100000000001</v>
       </c>
       <c r="D34" s="0">
         <v>83.527500000000003</v>
@@ -27082,10 +27082,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>83.659700000000001</v>
+        <v>83.681200000000004</v>
       </c>
       <c r="C35" s="0">
-        <v>38.103299999999997</v>
+        <v>37.846400000000003</v>
       </c>
       <c r="D35" s="0">
         <v>83.6815</v>
@@ -27839,10 +27839,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>83.787300000000002</v>
+        <v>83.737300000000005</v>
       </c>
       <c r="C36" s="0">
-        <v>38.194400000000002</v>
+        <v>38.249499999999998</v>
       </c>
       <c r="D36" s="0">
         <v>83.787300000000002</v>
@@ -28596,10 +28596,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>83.8095</v>
+        <v>83.865399999999994</v>
       </c>
       <c r="C37" s="0">
-        <v>37.9315</v>
+        <v>38.345599999999997</v>
       </c>
       <c r="D37" s="0">
         <v>83.815299999999993</v>
@@ -29353,10 +29353,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>83.674800000000005</v>
+        <v>83.724699999999999</v>
       </c>
       <c r="C38" s="0">
-        <v>37.3902</v>
+        <v>37.328800000000001</v>
       </c>
       <c r="D38" s="0">
         <v>83.674800000000005</v>
@@ -30110,10 +30110,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>83.652000000000001</v>
+        <v>83.549499999999995</v>
       </c>
       <c r="C39" s="0">
-        <v>36.024799999999999</v>
+        <v>36.168100000000003</v>
       </c>
       <c r="D39" s="0">
         <v>83.581900000000005</v>
@@ -30867,10 +30867,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>83.465800000000002</v>
+        <v>83.4953</v>
       </c>
       <c r="C40" s="0">
-        <v>34.473999999999997</v>
+        <v>34.655099999999997</v>
       </c>
       <c r="D40" s="0">
         <v>83.462800000000001</v>
@@ -31624,10 +31624,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>83.346900000000005</v>
+        <v>83.317099999999996</v>
       </c>
       <c r="C41" s="0">
-        <v>32.660200000000003</v>
+        <v>32.494799999999998</v>
       </c>
       <c r="D41" s="0">
         <v>83.346900000000005</v>
@@ -32387,7 +32387,7 @@
   <cols>
     <col min="1" max="1" width="74.5703125" customWidth="true"/>
     <col min="2" max="2" width="6" customWidth="true"/>
-    <col min="3" max="3" width="83.85546875" customWidth="true"/>
+    <col min="3" max="3" width="75.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
